--- a/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
+++ b/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
@@ -1,21 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\SoCDTtiNTY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\trans\SoCDTtiNTY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B539881-35F2-4ACF-93AE-EB11A251A4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{221672B5-0616-4C0D-A719-F2988D95ABA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26280" yWindow="2070" windowWidth="24420" windowHeight="14370" firstSheet="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="SoCDTtiNTY-psgr" sheetId="2" r:id="rId2"/>
-    <sheet name="SoCDTtiNTY-frgt" sheetId="4" r:id="rId3"/>
+    <sheet name="SoCDTtiNTY-psgr-LDV" sheetId="2" r:id="rId2"/>
+    <sheet name="SoCDTtiNTY-psgr-HDV" sheetId="6" r:id="rId3"/>
+    <sheet name="SoCDTtiNTY-psgr-aircraft" sheetId="5" r:id="rId4"/>
+    <sheet name="SoCDTtiNTY-psgr-rail" sheetId="7" r:id="rId5"/>
+    <sheet name="SoCDTtiNTY-psgr-ships" sheetId="8" r:id="rId6"/>
+    <sheet name="SoCDTtiNTY-psgr-motorbikes" sheetId="9" r:id="rId7"/>
+    <sheet name="SoCDTtiNTY-frgt-LDV" sheetId="10" r:id="rId8"/>
+    <sheet name="SoCDTtiNTY-frgt-HDV" sheetId="11" r:id="rId9"/>
+    <sheet name="SoCDTtiNTY-frgt-aircraft" sheetId="12" r:id="rId10"/>
+    <sheet name="SoCDTtiNTY-frgt-rail" sheetId="13" r:id="rId11"/>
+    <sheet name="SoCDTtiNTY-frgt-ships" sheetId="14" r:id="rId12"/>
+    <sheet name="SoCDTtiNTY-frgt-motorbikes" sheetId="15" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="20">
   <si>
     <t>SoCDTtiNTY Share of Cargo Dist Transported that is New This Year</t>
   </si>
@@ -69,24 +79,6 @@
   </si>
   <si>
     <t>vehicle lifetimes.</t>
-  </si>
-  <si>
-    <t>LDVs</t>
-  </si>
-  <si>
-    <t>HDVs</t>
-  </si>
-  <si>
-    <t>aircraft</t>
-  </si>
-  <si>
-    <t>rail</t>
-  </si>
-  <si>
-    <t>ships</t>
-  </si>
-  <si>
-    <t>motorbikes</t>
   </si>
   <si>
     <t>Share that is New (dimensionless)</t>
@@ -536,54 +528,2934 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B0403B3-2384-4589-8EF5-701D913B5895}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:AB8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" customWidth="1"/>
     <col min="2" max="8" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1">
+        <v>2024</v>
+      </c>
+      <c r="C1">
+        <v>2025</v>
+      </c>
+      <c r="D1">
+        <v>2026</v>
+      </c>
+      <c r="E1">
+        <v>2027</v>
+      </c>
+      <c r="F1">
+        <v>2028</v>
+      </c>
+      <c r="G1">
+        <v>2029</v>
+      </c>
+      <c r="H1">
+        <v>2030</v>
+      </c>
+      <c r="I1">
+        <v>2031</v>
+      </c>
+      <c r="J1">
+        <v>2032</v>
+      </c>
+      <c r="K1">
+        <v>2033</v>
+      </c>
+      <c r="L1">
+        <v>2034</v>
+      </c>
+      <c r="M1">
+        <v>2035</v>
+      </c>
+      <c r="N1">
+        <v>2036</v>
+      </c>
+      <c r="O1">
+        <v>2037</v>
+      </c>
+      <c r="P1">
+        <v>2038</v>
+      </c>
+      <c r="Q1">
+        <v>2039</v>
+      </c>
+      <c r="R1">
+        <v>2040</v>
+      </c>
+      <c r="S1">
+        <v>2041</v>
+      </c>
+      <c r="T1">
+        <v>2042</v>
+      </c>
+      <c r="U1">
+        <v>2043</v>
+      </c>
+      <c r="V1">
+        <v>2044</v>
+      </c>
+      <c r="W1">
+        <v>2045</v>
+      </c>
+      <c r="X1">
+        <v>2046</v>
+      </c>
+      <c r="Y1">
+        <v>2047</v>
+      </c>
+      <c r="Z1">
+        <v>2048</v>
+      </c>
+      <c r="AA1">
+        <v>2049</v>
+      </c>
+      <c r="AB1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="C2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="D2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="E2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="F2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="G2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="H2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="I2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="J2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="K2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="L2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="M2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="N2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="O2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="P2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="Q2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="R2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="S2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="T2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="U2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="V2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="W2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="X2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="Y2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="Z2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AA2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AB2">
+        <v>2.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="C3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="D3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="E3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="F3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="G3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="H3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="I3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="J3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="K3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="L3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="M3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="N3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="O3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="P3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="Q3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="R3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="S3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="T3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="U3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="V3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="W3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="X3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="Y3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="Z3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AA3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AB3">
+        <v>2.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="C4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="D4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="E4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="F4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="G4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="H4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="I4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="J4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="K4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="L4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="M4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="N4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="O4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="P4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="Q4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="R4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="S4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="T4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="U4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="V4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="W4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="X4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="Y4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="Z4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AA4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AB4">
+        <v>2.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="C5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="D5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="E5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="F5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="G5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="H5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="I5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="J5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="K5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="L5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="M5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="N5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="O5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="P5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="Q5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="R5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="S5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="T5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="U5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="V5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="W5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="X5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="Y5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="Z5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AA5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AB5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="C6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="D6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="E6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="F6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="G6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="H6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="I6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="J6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="K6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="L6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="M6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="N6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="O6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="P6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="Q6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="R6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="S6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="T6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="U6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="V6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="W6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="X6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="Y6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="Z6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AA6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AB6">
+        <v>2.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="C7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="D7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="E7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="F7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="G7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="H7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="I7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="J7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="K7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="L7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="M7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="N7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="O7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="P7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="Q7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="R7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="S7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="T7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="U7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="V7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="W7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="X7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="Y7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="Z7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AA7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AB7">
+        <v>2.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="C8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="D8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="E8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="F8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="G8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="H8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="I8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="J8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="K8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="L8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="M8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="N8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="O8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="P8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="Q8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="R8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="S8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="T8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="U8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="V8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="W8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="X8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="Y8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="Z8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AA8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AB8">
+        <v>2.8000000000000001E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01DB5866-1262-4C8A-989A-6F1B656D2B6C}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:AB8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="8" width="14.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>12</v>
+      </c>
+      <c r="B1">
+        <v>2024</v>
+      </c>
+      <c r="C1">
+        <v>2025</v>
+      </c>
+      <c r="D1">
+        <v>2026</v>
+      </c>
+      <c r="E1">
+        <v>2027</v>
+      </c>
+      <c r="F1">
+        <v>2028</v>
+      </c>
+      <c r="G1">
+        <v>2029</v>
+      </c>
+      <c r="H1">
+        <v>2030</v>
+      </c>
+      <c r="I1">
+        <v>2031</v>
+      </c>
+      <c r="J1">
+        <v>2032</v>
+      </c>
+      <c r="K1">
+        <v>2033</v>
+      </c>
+      <c r="L1">
+        <v>2034</v>
+      </c>
+      <c r="M1">
+        <v>2035</v>
+      </c>
+      <c r="N1">
+        <v>2036</v>
+      </c>
+      <c r="O1">
+        <v>2037</v>
+      </c>
+      <c r="P1">
+        <v>2038</v>
+      </c>
+      <c r="Q1">
+        <v>2039</v>
+      </c>
+      <c r="R1">
+        <v>2040</v>
+      </c>
+      <c r="S1">
+        <v>2041</v>
+      </c>
+      <c r="T1">
+        <v>2042</v>
+      </c>
+      <c r="U1">
+        <v>2043</v>
+      </c>
+      <c r="V1">
+        <v>2044</v>
+      </c>
+      <c r="W1">
+        <v>2045</v>
+      </c>
+      <c r="X1">
+        <v>2046</v>
+      </c>
+      <c r="Y1">
+        <v>2047</v>
+      </c>
+      <c r="Z1">
+        <v>2048</v>
+      </c>
+      <c r="AA1">
+        <v>2049</v>
+      </c>
+      <c r="AB1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="D2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="E2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="F2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="G2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="H2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="I2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="J2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="K2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="L2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="M2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="N2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="O2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="P2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Q2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="R2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="S2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="T2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="U2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="V2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="W2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="X2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Y2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Z2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AA2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AB2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="D3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="E3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="F3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="G3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="H3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="I3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="J3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="K3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="L3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="M3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="N3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="O3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="P3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Q3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="R3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="S3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="T3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="U3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="V3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="W3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="X3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Y3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Z3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AA3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AB3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="D4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="E4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="F4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="G4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="H4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="I4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="J4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="K4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="L4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="M4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="N4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="O4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="P4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Q4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="R4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="S4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="T4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="U4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="V4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="W4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="X4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Y4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Z4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AA4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AB4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="D5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="E5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="F5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="G5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="H5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="I5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="J5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="K5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="L5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="M5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="N5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="O5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="P5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Q5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="R5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="S5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="T5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="U5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="V5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="W5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="X5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Y5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Z5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AA5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AB5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="D6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="E6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="F6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="G6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="H6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="I6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="J6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="K6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="L6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="M6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="N6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="O6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="P6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Q6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="R6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="S6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="T6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="U6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="V6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="W6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="X6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Y6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Z6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AA6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AB6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="D7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="E7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="F7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="G7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="H7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="I7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="J7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="K7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="L7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="M7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="N7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="O7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="P7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Q7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="R7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="S7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="T7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="U7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="V7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="W7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="X7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Y7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Z7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AA7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AB7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="D8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="E8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="F8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="G8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="H8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="I8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="J8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="K8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="L8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="M8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="N8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="O8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="P8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Q8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="R8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="S8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="T8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="U8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="V8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="W8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="X8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Y8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Z8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AA8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AB8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7326473-2A87-4A11-807E-F41DA42C047C}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:AB8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="8" width="14.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1">
+        <v>2024</v>
+      </c>
+      <c r="C1">
+        <v>2025</v>
+      </c>
+      <c r="D1">
+        <v>2026</v>
+      </c>
+      <c r="E1">
+        <v>2027</v>
+      </c>
+      <c r="F1">
+        <v>2028</v>
+      </c>
+      <c r="G1">
+        <v>2029</v>
+      </c>
+      <c r="H1">
+        <v>2030</v>
+      </c>
+      <c r="I1">
+        <v>2031</v>
+      </c>
+      <c r="J1">
+        <v>2032</v>
+      </c>
+      <c r="K1">
+        <v>2033</v>
+      </c>
+      <c r="L1">
+        <v>2034</v>
+      </c>
+      <c r="M1">
+        <v>2035</v>
+      </c>
+      <c r="N1">
+        <v>2036</v>
+      </c>
+      <c r="O1">
+        <v>2037</v>
+      </c>
+      <c r="P1">
+        <v>2038</v>
+      </c>
+      <c r="Q1">
+        <v>2039</v>
+      </c>
+      <c r="R1">
+        <v>2040</v>
+      </c>
+      <c r="S1">
+        <v>2041</v>
+      </c>
+      <c r="T1">
+        <v>2042</v>
+      </c>
+      <c r="U1">
+        <v>2043</v>
+      </c>
+      <c r="V1">
+        <v>2044</v>
+      </c>
+      <c r="W1">
+        <v>2045</v>
+      </c>
+      <c r="X1">
+        <v>2046</v>
+      </c>
+      <c r="Y1">
+        <v>2047</v>
+      </c>
+      <c r="Z1">
+        <v>2048</v>
+      </c>
+      <c r="AA1">
+        <v>2049</v>
+      </c>
+      <c r="AB1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="C2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="D2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="E2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="F2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="G2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="H2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="I2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="J2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="K2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="L2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="M2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="N2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="O2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="P2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="Q2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="R2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="S2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="T2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="U2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="V2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="W2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="X2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="Y2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="Z2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="AA2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="AB2">
+        <v>3.0300000000000001E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="C3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="D3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="E3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="F3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="G3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="H3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="I3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="J3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="K3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="L3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="M3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="N3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="O3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="P3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="Q3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="R3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="S3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="T3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="U3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="V3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="W3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="X3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="Y3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="Z3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="AA3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="AB3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="C4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="D4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="E4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="F4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="G4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="H4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="I4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="J4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="K4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="L4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="M4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="N4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="O4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="P4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="Q4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="R4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="S4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="T4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="U4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="V4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="W4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="X4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="Y4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="Z4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="AA4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="AB4">
+        <v>3.0300000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="C5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="D5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="E5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="F5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="G5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="H5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="I5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="J5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="K5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="L5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="M5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="N5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="O5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="P5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="Q5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="R5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="S5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="T5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="U5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="V5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="W5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="X5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="Y5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="Z5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="AA5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="AB5">
+        <v>3.0300000000000001E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="C6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="D6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="E6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="F6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="G6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="H6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="I6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="J6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="K6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="L6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="M6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="N6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="O6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="P6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="Q6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="R6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="S6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="T6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="U6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="V6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="W6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="X6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="Y6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="Z6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="AA6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="AB6">
+        <v>3.0300000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="C7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="D7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="E7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="F7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="G7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="H7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="I7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="J7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="K7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="L7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="M7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="N7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="O7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="P7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="Q7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="R7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="S7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="T7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="U7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="V7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="W7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="X7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="Y7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="Z7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="AA7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="AB7">
+        <v>3.0300000000000001E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="C8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="D8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="E8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="F8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="G8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="H8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="I8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="J8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="K8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="L8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="M8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="N8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="O8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="P8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="Q8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="R8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="S8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="T8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="U8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="V8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="W8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="X8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="Y8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="Z8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="AA8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="AB8">
+        <v>3.0300000000000001E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70D3F9B9-404F-41C4-A106-523DBAC3F7EF}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:AB8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="8" width="14.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1">
+        <v>2024</v>
+      </c>
+      <c r="C1">
+        <v>2025</v>
+      </c>
+      <c r="D1">
+        <v>2026</v>
+      </c>
+      <c r="E1">
+        <v>2027</v>
+      </c>
+      <c r="F1">
+        <v>2028</v>
+      </c>
+      <c r="G1">
+        <v>2029</v>
+      </c>
+      <c r="H1">
+        <v>2030</v>
+      </c>
+      <c r="I1">
+        <v>2031</v>
+      </c>
+      <c r="J1">
+        <v>2032</v>
+      </c>
+      <c r="K1">
+        <v>2033</v>
+      </c>
+      <c r="L1">
+        <v>2034</v>
+      </c>
+      <c r="M1">
+        <v>2035</v>
+      </c>
+      <c r="N1">
+        <v>2036</v>
+      </c>
+      <c r="O1">
+        <v>2037</v>
+      </c>
+      <c r="P1">
+        <v>2038</v>
+      </c>
+      <c r="Q1">
+        <v>2039</v>
+      </c>
+      <c r="R1">
+        <v>2040</v>
+      </c>
+      <c r="S1">
+        <v>2041</v>
+      </c>
+      <c r="T1">
+        <v>2042</v>
+      </c>
+      <c r="U1">
+        <v>2043</v>
+      </c>
+      <c r="V1">
+        <v>2044</v>
+      </c>
+      <c r="W1">
+        <v>2045</v>
+      </c>
+      <c r="X1">
+        <v>2046</v>
+      </c>
+      <c r="Y1">
+        <v>2047</v>
+      </c>
+      <c r="Z1">
+        <v>2048</v>
+      </c>
+      <c r="AA1">
+        <v>2049</v>
+      </c>
+      <c r="AB1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:AB8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="8" width="14.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1">
+        <v>2024</v>
+      </c>
+      <c r="C1">
+        <v>2025</v>
+      </c>
+      <c r="D1">
+        <v>2026</v>
+      </c>
+      <c r="E1">
+        <v>2027</v>
+      </c>
+      <c r="F1">
+        <v>2028</v>
+      </c>
+      <c r="G1">
+        <v>2029</v>
+      </c>
+      <c r="H1">
+        <v>2030</v>
+      </c>
+      <c r="I1">
+        <v>2031</v>
+      </c>
+      <c r="J1">
+        <v>2032</v>
+      </c>
+      <c r="K1">
+        <v>2033</v>
+      </c>
+      <c r="L1">
+        <v>2034</v>
+      </c>
+      <c r="M1">
+        <v>2035</v>
+      </c>
+      <c r="N1">
+        <v>2036</v>
+      </c>
+      <c r="O1">
+        <v>2037</v>
+      </c>
+      <c r="P1">
+        <v>2038</v>
+      </c>
+      <c r="Q1">
+        <v>2039</v>
+      </c>
+      <c r="R1">
+        <v>2040</v>
+      </c>
+      <c r="S1">
+        <v>2041</v>
+      </c>
+      <c r="T1">
+        <v>2042</v>
+      </c>
+      <c r="U1">
+        <v>2043</v>
+      </c>
+      <c r="V1">
+        <v>2044</v>
+      </c>
+      <c r="W1">
+        <v>2045</v>
+      </c>
+      <c r="X1">
+        <v>2046</v>
+      </c>
+      <c r="Y1">
+        <v>2047</v>
+      </c>
+      <c r="Z1">
+        <v>2048</v>
+      </c>
+      <c r="AA1">
+        <v>2049</v>
+      </c>
+      <c r="AB1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="B2">
         <f>1/17</f>
         <v>5.8823529411764705E-2</v>
       </c>
       <c r="C2">
-        <f t="shared" ref="C2:H2" si="0">1/17</f>
+        <f t="shared" ref="C2:AB8" si="0">1/17</f>
         <v>5.8823529411764705E-2</v>
       </c>
       <c r="D2">
@@ -606,135 +3478,763 @@
         <f t="shared" si="0"/>
         <v>5.8823529411764705E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>13</v>
+      <c r="I2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="J2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="K2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="L2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="M2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="N2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="O2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="P2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Q2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="R2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="S2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="T2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="U2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="V2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="W2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="X2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Y2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Z2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AA2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AB2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="B3">
-        <v>0.09</v>
+        <f>1/17</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="C3">
-        <v>0.09</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="D3">
-        <v>0.09</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="E3">
-        <v>0.09</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="F3">
-        <v>0.09</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="G3">
-        <v>0.09</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="H3">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="I3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="J3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="K3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="L3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="M3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="N3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="O3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="P3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="R3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="S3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="T3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="U3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="V3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="W3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="X3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Y3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Z3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AA3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AB3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="B4">
-        <v>4.1599999999999998E-2</v>
+        <f>1/17</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="C4">
-        <v>4.1599999999999998E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="D4">
-        <v>4.1599999999999998E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="E4">
-        <v>4.1599999999999998E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="F4">
-        <v>4.1599999999999998E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="G4">
-        <v>4.1599999999999998E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="H4">
-        <v>4.1599999999999998E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>15</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="P4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="S4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="V4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="W4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="X4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Y4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Z4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AA4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AB4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="B5">
-        <v>2.9000000000000001E-2</v>
+        <f>1/17</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="C5">
-        <v>2.9000000000000001E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="D5">
-        <v>2.9000000000000001E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="E5">
-        <v>2.9000000000000001E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="F5">
-        <v>2.9000000000000001E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="G5">
-        <v>2.9000000000000001E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="H5">
-        <v>2.9000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>16</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="W5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="X5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Y5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Z5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AA5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AB5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="B6">
-        <v>2.9819999999999999E-2</v>
+        <f>1/17</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="C6">
-        <v>2.9819999999999999E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="D6">
-        <v>2.9819999999999999E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="E6">
-        <v>2.9819999999999999E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="F6">
-        <v>2.9819999999999999E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="G6">
-        <v>2.9819999999999999E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="H6">
-        <v>2.9819999999999999E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>17</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="W6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="X6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Y6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Z6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AA6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AB6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="B7">
-        <v>5.8500000000000003E-2</v>
+        <f>1/17</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="C7">
-        <v>5.8500000000000003E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="D7">
-        <v>5.8500000000000003E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="E7">
-        <v>5.8500000000000003E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="F7">
-        <v>5.8500000000000003E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="G7">
-        <v>5.8500000000000003E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="H7">
-        <v>5.8500000000000003E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="W7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="X7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Y7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Z7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AA7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AB7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <f>1/17</f>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="X8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Z8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AA8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AB8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
     </row>
   </sheetData>
@@ -743,53 +4243,3638 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{276CFCC7-3C65-4C8A-9570-8ABD8275E960}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:AB8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" customWidth="1"/>
     <col min="2" max="8" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1">
+        <v>2024</v>
+      </c>
+      <c r="C1">
+        <v>2025</v>
+      </c>
+      <c r="D1">
+        <v>2026</v>
+      </c>
+      <c r="E1">
+        <v>2027</v>
+      </c>
+      <c r="F1">
+        <v>2028</v>
+      </c>
+      <c r="G1">
+        <v>2029</v>
+      </c>
+      <c r="H1">
+        <v>2030</v>
+      </c>
+      <c r="I1">
+        <v>2031</v>
+      </c>
+      <c r="J1">
+        <v>2032</v>
+      </c>
+      <c r="K1">
+        <v>2033</v>
+      </c>
+      <c r="L1">
+        <v>2034</v>
+      </c>
+      <c r="M1">
+        <v>2035</v>
+      </c>
+      <c r="N1">
+        <v>2036</v>
+      </c>
+      <c r="O1">
+        <v>2037</v>
+      </c>
+      <c r="P1">
+        <v>2038</v>
+      </c>
+      <c r="Q1">
+        <v>2039</v>
+      </c>
+      <c r="R1">
+        <v>2040</v>
+      </c>
+      <c r="S1">
+        <v>2041</v>
+      </c>
+      <c r="T1">
+        <v>2042</v>
+      </c>
+      <c r="U1">
+        <v>2043</v>
+      </c>
+      <c r="V1">
+        <v>2044</v>
+      </c>
+      <c r="W1">
+        <v>2045</v>
+      </c>
+      <c r="X1">
+        <v>2046</v>
+      </c>
+      <c r="Y1">
+        <v>2047</v>
+      </c>
+      <c r="Z1">
+        <v>2048</v>
+      </c>
+      <c r="AA1">
+        <v>2049</v>
+      </c>
+      <c r="AB1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
+        <v>0.09</v>
+      </c>
+      <c r="C2">
+        <v>0.09</v>
+      </c>
+      <c r="D2">
+        <v>0.09</v>
+      </c>
+      <c r="E2">
+        <v>0.09</v>
+      </c>
+      <c r="F2">
+        <v>0.09</v>
+      </c>
+      <c r="G2">
+        <v>0.09</v>
+      </c>
+      <c r="H2">
+        <v>0.09</v>
+      </c>
+      <c r="I2">
+        <v>0.09</v>
+      </c>
+      <c r="J2">
+        <v>0.09</v>
+      </c>
+      <c r="K2">
+        <v>0.09</v>
+      </c>
+      <c r="L2">
+        <v>0.09</v>
+      </c>
+      <c r="M2">
+        <v>0.09</v>
+      </c>
+      <c r="N2">
+        <v>0.09</v>
+      </c>
+      <c r="O2">
+        <v>0.09</v>
+      </c>
+      <c r="P2">
+        <v>0.09</v>
+      </c>
+      <c r="Q2">
+        <v>0.09</v>
+      </c>
+      <c r="R2">
+        <v>0.09</v>
+      </c>
+      <c r="S2">
+        <v>0.09</v>
+      </c>
+      <c r="T2">
+        <v>0.09</v>
+      </c>
+      <c r="U2">
+        <v>0.09</v>
+      </c>
+      <c r="V2">
+        <v>0.09</v>
+      </c>
+      <c r="W2">
+        <v>0.09</v>
+      </c>
+      <c r="X2">
+        <v>0.09</v>
+      </c>
+      <c r="Y2">
+        <v>0.09</v>
+      </c>
+      <c r="Z2">
+        <v>0.09</v>
+      </c>
+      <c r="AA2">
+        <v>0.09</v>
+      </c>
+      <c r="AB2">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>0.09</v>
+      </c>
+      <c r="C3">
+        <v>0.09</v>
+      </c>
+      <c r="D3">
+        <v>0.09</v>
+      </c>
+      <c r="E3">
+        <v>0.09</v>
+      </c>
+      <c r="F3">
+        <v>0.09</v>
+      </c>
+      <c r="G3">
+        <v>0.09</v>
+      </c>
+      <c r="H3">
+        <v>0.09</v>
+      </c>
+      <c r="I3">
+        <v>0.09</v>
+      </c>
+      <c r="J3">
+        <v>0.09</v>
+      </c>
+      <c r="K3">
+        <v>0.09</v>
+      </c>
+      <c r="L3">
+        <v>0.09</v>
+      </c>
+      <c r="M3">
+        <v>0.09</v>
+      </c>
+      <c r="N3">
+        <v>0.09</v>
+      </c>
+      <c r="O3">
+        <v>0.09</v>
+      </c>
+      <c r="P3">
+        <v>0.09</v>
+      </c>
+      <c r="Q3">
+        <v>0.09</v>
+      </c>
+      <c r="R3">
+        <v>0.09</v>
+      </c>
+      <c r="S3">
+        <v>0.09</v>
+      </c>
+      <c r="T3">
+        <v>0.09</v>
+      </c>
+      <c r="U3">
+        <v>0.09</v>
+      </c>
+      <c r="V3">
+        <v>0.09</v>
+      </c>
+      <c r="W3">
+        <v>0.09</v>
+      </c>
+      <c r="X3">
+        <v>0.09</v>
+      </c>
+      <c r="Y3">
+        <v>0.09</v>
+      </c>
+      <c r="Z3">
+        <v>0.09</v>
+      </c>
+      <c r="AA3">
+        <v>0.09</v>
+      </c>
+      <c r="AB3">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <v>0.09</v>
+      </c>
+      <c r="C4">
+        <v>0.09</v>
+      </c>
+      <c r="D4">
+        <v>0.09</v>
+      </c>
+      <c r="E4">
+        <v>0.09</v>
+      </c>
+      <c r="F4">
+        <v>0.09</v>
+      </c>
+      <c r="G4">
+        <v>0.09</v>
+      </c>
+      <c r="H4">
+        <v>0.09</v>
+      </c>
+      <c r="I4">
+        <v>0.09</v>
+      </c>
+      <c r="J4">
+        <v>0.09</v>
+      </c>
+      <c r="K4">
+        <v>0.09</v>
+      </c>
+      <c r="L4">
+        <v>0.09</v>
+      </c>
+      <c r="M4">
+        <v>0.09</v>
+      </c>
+      <c r="N4">
+        <v>0.09</v>
+      </c>
+      <c r="O4">
+        <v>0.09</v>
+      </c>
+      <c r="P4">
+        <v>0.09</v>
+      </c>
+      <c r="Q4">
+        <v>0.09</v>
+      </c>
+      <c r="R4">
+        <v>0.09</v>
+      </c>
+      <c r="S4">
+        <v>0.09</v>
+      </c>
+      <c r="T4">
+        <v>0.09</v>
+      </c>
+      <c r="U4">
+        <v>0.09</v>
+      </c>
+      <c r="V4">
+        <v>0.09</v>
+      </c>
+      <c r="W4">
+        <v>0.09</v>
+      </c>
+      <c r="X4">
+        <v>0.09</v>
+      </c>
+      <c r="Y4">
+        <v>0.09</v>
+      </c>
+      <c r="Z4">
+        <v>0.09</v>
+      </c>
+      <c r="AA4">
+        <v>0.09</v>
+      </c>
+      <c r="AB4">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>0.09</v>
+      </c>
+      <c r="C5">
+        <v>0.09</v>
+      </c>
+      <c r="D5">
+        <v>0.09</v>
+      </c>
+      <c r="E5">
+        <v>0.09</v>
+      </c>
+      <c r="F5">
+        <v>0.09</v>
+      </c>
+      <c r="G5">
+        <v>0.09</v>
+      </c>
+      <c r="H5">
+        <v>0.09</v>
+      </c>
+      <c r="I5">
+        <v>0.09</v>
+      </c>
+      <c r="J5">
+        <v>0.09</v>
+      </c>
+      <c r="K5">
+        <v>0.09</v>
+      </c>
+      <c r="L5">
+        <v>0.09</v>
+      </c>
+      <c r="M5">
+        <v>0.09</v>
+      </c>
+      <c r="N5">
+        <v>0.09</v>
+      </c>
+      <c r="O5">
+        <v>0.09</v>
+      </c>
+      <c r="P5">
+        <v>0.09</v>
+      </c>
+      <c r="Q5">
+        <v>0.09</v>
+      </c>
+      <c r="R5">
+        <v>0.09</v>
+      </c>
+      <c r="S5">
+        <v>0.09</v>
+      </c>
+      <c r="T5">
+        <v>0.09</v>
+      </c>
+      <c r="U5">
+        <v>0.09</v>
+      </c>
+      <c r="V5">
+        <v>0.09</v>
+      </c>
+      <c r="W5">
+        <v>0.09</v>
+      </c>
+      <c r="X5">
+        <v>0.09</v>
+      </c>
+      <c r="Y5">
+        <v>0.09</v>
+      </c>
+      <c r="Z5">
+        <v>0.09</v>
+      </c>
+      <c r="AA5">
+        <v>0.09</v>
+      </c>
+      <c r="AB5">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
+        <v>0.09</v>
+      </c>
+      <c r="C6">
+        <v>0.09</v>
+      </c>
+      <c r="D6">
+        <v>0.09</v>
+      </c>
+      <c r="E6">
+        <v>0.09</v>
+      </c>
+      <c r="F6">
+        <v>0.09</v>
+      </c>
+      <c r="G6">
+        <v>0.09</v>
+      </c>
+      <c r="H6">
+        <v>0.09</v>
+      </c>
+      <c r="I6">
+        <v>0.09</v>
+      </c>
+      <c r="J6">
+        <v>0.09</v>
+      </c>
+      <c r="K6">
+        <v>0.09</v>
+      </c>
+      <c r="L6">
+        <v>0.09</v>
+      </c>
+      <c r="M6">
+        <v>0.09</v>
+      </c>
+      <c r="N6">
+        <v>0.09</v>
+      </c>
+      <c r="O6">
+        <v>0.09</v>
+      </c>
+      <c r="P6">
+        <v>0.09</v>
+      </c>
+      <c r="Q6">
+        <v>0.09</v>
+      </c>
+      <c r="R6">
+        <v>0.09</v>
+      </c>
+      <c r="S6">
+        <v>0.09</v>
+      </c>
+      <c r="T6">
+        <v>0.09</v>
+      </c>
+      <c r="U6">
+        <v>0.09</v>
+      </c>
+      <c r="V6">
+        <v>0.09</v>
+      </c>
+      <c r="W6">
+        <v>0.09</v>
+      </c>
+      <c r="X6">
+        <v>0.09</v>
+      </c>
+      <c r="Y6">
+        <v>0.09</v>
+      </c>
+      <c r="Z6">
+        <v>0.09</v>
+      </c>
+      <c r="AA6">
+        <v>0.09</v>
+      </c>
+      <c r="AB6">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B7">
+        <v>0.09</v>
+      </c>
+      <c r="C7">
+        <v>0.09</v>
+      </c>
+      <c r="D7">
+        <v>0.09</v>
+      </c>
+      <c r="E7">
+        <v>0.09</v>
+      </c>
+      <c r="F7">
+        <v>0.09</v>
+      </c>
+      <c r="G7">
+        <v>0.09</v>
+      </c>
+      <c r="H7">
+        <v>0.09</v>
+      </c>
+      <c r="I7">
+        <v>0.09</v>
+      </c>
+      <c r="J7">
+        <v>0.09</v>
+      </c>
+      <c r="K7">
+        <v>0.09</v>
+      </c>
+      <c r="L7">
+        <v>0.09</v>
+      </c>
+      <c r="M7">
+        <v>0.09</v>
+      </c>
+      <c r="N7">
+        <v>0.09</v>
+      </c>
+      <c r="O7">
+        <v>0.09</v>
+      </c>
+      <c r="P7">
+        <v>0.09</v>
+      </c>
+      <c r="Q7">
+        <v>0.09</v>
+      </c>
+      <c r="R7">
+        <v>0.09</v>
+      </c>
+      <c r="S7">
+        <v>0.09</v>
+      </c>
+      <c r="T7">
+        <v>0.09</v>
+      </c>
+      <c r="U7">
+        <v>0.09</v>
+      </c>
+      <c r="V7">
+        <v>0.09</v>
+      </c>
+      <c r="W7">
+        <v>0.09</v>
+      </c>
+      <c r="X7">
+        <v>0.09</v>
+      </c>
+      <c r="Y7">
+        <v>0.09</v>
+      </c>
+      <c r="Z7">
+        <v>0.09</v>
+      </c>
+      <c r="AA7">
+        <v>0.09</v>
+      </c>
+      <c r="AB7">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B8">
+        <v>0.09</v>
+      </c>
+      <c r="C8">
+        <v>0.09</v>
+      </c>
+      <c r="D8">
+        <v>0.09</v>
+      </c>
+      <c r="E8">
+        <v>0.09</v>
+      </c>
+      <c r="F8">
+        <v>0.09</v>
+      </c>
+      <c r="G8">
+        <v>0.09</v>
+      </c>
+      <c r="H8">
+        <v>0.09</v>
+      </c>
+      <c r="I8">
+        <v>0.09</v>
+      </c>
+      <c r="J8">
+        <v>0.09</v>
+      </c>
+      <c r="K8">
+        <v>0.09</v>
+      </c>
+      <c r="L8">
+        <v>0.09</v>
+      </c>
+      <c r="M8">
+        <v>0.09</v>
+      </c>
+      <c r="N8">
+        <v>0.09</v>
+      </c>
+      <c r="O8">
+        <v>0.09</v>
+      </c>
+      <c r="P8">
+        <v>0.09</v>
+      </c>
+      <c r="Q8">
+        <v>0.09</v>
+      </c>
+      <c r="R8">
+        <v>0.09</v>
+      </c>
+      <c r="S8">
+        <v>0.09</v>
+      </c>
+      <c r="T8">
+        <v>0.09</v>
+      </c>
+      <c r="U8">
+        <v>0.09</v>
+      </c>
+      <c r="V8">
+        <v>0.09</v>
+      </c>
+      <c r="W8">
+        <v>0.09</v>
+      </c>
+      <c r="X8">
+        <v>0.09</v>
+      </c>
+      <c r="Y8">
+        <v>0.09</v>
+      </c>
+      <c r="Z8">
+        <v>0.09</v>
+      </c>
+      <c r="AA8">
+        <v>0.09</v>
+      </c>
+      <c r="AB8">
+        <v>0.09</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B88A4EA-47CE-42D5-AFB7-375DAA5184C2}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:AB8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="8" width="14.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>12</v>
+      </c>
+      <c r="B1">
+        <v>2024</v>
+      </c>
+      <c r="C1">
+        <v>2025</v>
+      </c>
+      <c r="D1">
+        <v>2026</v>
+      </c>
+      <c r="E1">
+        <v>2027</v>
+      </c>
+      <c r="F1">
+        <v>2028</v>
+      </c>
+      <c r="G1">
+        <v>2029</v>
+      </c>
+      <c r="H1">
+        <v>2030</v>
+      </c>
+      <c r="I1">
+        <v>2031</v>
+      </c>
+      <c r="J1">
+        <v>2032</v>
+      </c>
+      <c r="K1">
+        <v>2033</v>
+      </c>
+      <c r="L1">
+        <v>2034</v>
+      </c>
+      <c r="M1">
+        <v>2035</v>
+      </c>
+      <c r="N1">
+        <v>2036</v>
+      </c>
+      <c r="O1">
+        <v>2037</v>
+      </c>
+      <c r="P1">
+        <v>2038</v>
+      </c>
+      <c r="Q1">
+        <v>2039</v>
+      </c>
+      <c r="R1">
+        <v>2040</v>
+      </c>
+      <c r="S1">
+        <v>2041</v>
+      </c>
+      <c r="T1">
+        <v>2042</v>
+      </c>
+      <c r="U1">
+        <v>2043</v>
+      </c>
+      <c r="V1">
+        <v>2044</v>
+      </c>
+      <c r="W1">
+        <v>2045</v>
+      </c>
+      <c r="X1">
+        <v>2046</v>
+      </c>
+      <c r="Y1">
+        <v>2047</v>
+      </c>
+      <c r="Z1">
+        <v>2048</v>
+      </c>
+      <c r="AA1">
+        <v>2049</v>
+      </c>
+      <c r="AB1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="C2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="D2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="E2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="F2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="G2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="H2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="I2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="J2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="K2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="L2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="M2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="N2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="O2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="P2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="Q2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="R2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="S2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="T2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="U2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="V2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="W2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="X2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="Y2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="Z2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="AA2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="AB2">
+        <v>4.1599999999999998E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="C3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="D3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="E3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="F3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="G3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="H3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="I3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="J3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="K3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="L3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="M3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="N3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="O3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="P3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="Q3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="R3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="S3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="T3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="U3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="V3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="W3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="X3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="Y3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="Z3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="AA3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="AB3">
+        <v>4.1599999999999998E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="C4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="D4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="E4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="F4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="G4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="H4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="I4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="J4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="K4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="L4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="M4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="N4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="O4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="P4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="Q4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="R4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="S4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="T4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="U4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="V4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="W4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="X4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="Y4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="Z4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="AA4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="AB4">
+        <v>4.1599999999999998E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="C5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="D5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="E5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="F5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="G5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="H5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="I5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="J5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="K5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="L5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="M5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="N5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="O5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="P5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="Q5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="R5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="S5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="T5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="U5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="V5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="W5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="X5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="Y5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="Z5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="AA5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="AB5">
+        <v>4.1599999999999998E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="C6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="D6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="E6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="F6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="G6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="H6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="I6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="J6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="K6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="L6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="M6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="N6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="O6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="P6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="Q6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="R6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="S6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="T6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="U6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="V6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="W6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="X6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="Y6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="Z6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="AA6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="AB6">
+        <v>4.1599999999999998E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="C7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="D7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="E7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="F7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="G7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="H7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="I7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="J7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="K7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="L7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="M7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="N7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="O7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="P7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="Q7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="R7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="S7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="T7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="U7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="V7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="W7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="X7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="Y7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="Z7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="AA7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="AB7">
+        <v>4.1599999999999998E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="C8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="D8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="E8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="F8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="G8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="H8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="I8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="J8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="K8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="L8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="M8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="N8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="O8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="P8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="Q8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="R8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="S8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="T8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="U8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="V8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="W8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="X8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="Y8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="Z8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="AA8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="AB8">
+        <v>4.1599999999999998E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9D487B5-BD92-41CD-8C5F-22D334D60FD8}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:AB8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="8" width="14.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1">
+        <v>2024</v>
+      </c>
+      <c r="C1">
+        <v>2025</v>
+      </c>
+      <c r="D1">
+        <v>2026</v>
+      </c>
+      <c r="E1">
+        <v>2027</v>
+      </c>
+      <c r="F1">
+        <v>2028</v>
+      </c>
+      <c r="G1">
+        <v>2029</v>
+      </c>
+      <c r="H1">
+        <v>2030</v>
+      </c>
+      <c r="I1">
+        <v>2031</v>
+      </c>
+      <c r="J1">
+        <v>2032</v>
+      </c>
+      <c r="K1">
+        <v>2033</v>
+      </c>
+      <c r="L1">
+        <v>2034</v>
+      </c>
+      <c r="M1">
+        <v>2035</v>
+      </c>
+      <c r="N1">
+        <v>2036</v>
+      </c>
+      <c r="O1">
+        <v>2037</v>
+      </c>
+      <c r="P1">
+        <v>2038</v>
+      </c>
+      <c r="Q1">
+        <v>2039</v>
+      </c>
+      <c r="R1">
+        <v>2040</v>
+      </c>
+      <c r="S1">
+        <v>2041</v>
+      </c>
+      <c r="T1">
+        <v>2042</v>
+      </c>
+      <c r="U1">
+        <v>2043</v>
+      </c>
+      <c r="V1">
+        <v>2044</v>
+      </c>
+      <c r="W1">
+        <v>2045</v>
+      </c>
+      <c r="X1">
+        <v>2046</v>
+      </c>
+      <c r="Y1">
+        <v>2047</v>
+      </c>
+      <c r="Z1">
+        <v>2048</v>
+      </c>
+      <c r="AA1">
+        <v>2049</v>
+      </c>
+      <c r="AB1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="D2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="E2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="F2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="G2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="H2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="I2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="J2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="K2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="L2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="M2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="N2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="O2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="P2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Q2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="R2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="S2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="T2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="U2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="V2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="W2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="X2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Y2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Z2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AA2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AB2">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="D3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="E3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="F3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="G3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="H3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="I3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="J3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="K3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="L3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="M3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="N3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="O3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="P3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Q3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="R3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="S3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="T3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="U3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="V3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="W3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="X3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Y3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Z3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AA3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AB3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="D4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="E4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="F4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="G4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="H4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="I4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="J4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="K4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="L4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="M4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="N4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="O4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="P4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Q4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="R4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="S4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="T4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="U4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="V4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="W4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="X4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Y4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Z4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AA4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AB4">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="D5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="E5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="F5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="G5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="H5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="I5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="J5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="K5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="L5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="M5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="N5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="O5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="P5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Q5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="R5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="S5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="T5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="U5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="V5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="W5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="X5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Y5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Z5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AA5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AB5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="D6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="E6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="F6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="G6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="H6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="I6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="J6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="K6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="L6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="M6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="N6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="O6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="P6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Q6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="R6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="S6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="T6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="U6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="V6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="W6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="X6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Y6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Z6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AA6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AB6">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="D7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="E7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="F7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="G7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="H7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="I7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="J7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="K7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="L7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="M7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="N7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="O7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="P7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Q7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="R7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="S7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="T7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="U7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="V7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="W7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="X7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Y7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Z7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AA7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AB7">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="C8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="D8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="E8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="F8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="G8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="H8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="I8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="J8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="K8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="L8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="M8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="N8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="O8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="P8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Q8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="R8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="S8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="T8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="U8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="V8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="W8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="X8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Y8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Z8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AA8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="AB8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF50EAB6-F746-42D3-B7C6-492FB2C1F960}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:AB8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="8" width="14.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1">
+        <v>2024</v>
+      </c>
+      <c r="C1">
+        <v>2025</v>
+      </c>
+      <c r="D1">
+        <v>2026</v>
+      </c>
+      <c r="E1">
+        <v>2027</v>
+      </c>
+      <c r="F1">
+        <v>2028</v>
+      </c>
+      <c r="G1">
+        <v>2029</v>
+      </c>
+      <c r="H1">
+        <v>2030</v>
+      </c>
+      <c r="I1">
+        <v>2031</v>
+      </c>
+      <c r="J1">
+        <v>2032</v>
+      </c>
+      <c r="K1">
+        <v>2033</v>
+      </c>
+      <c r="L1">
+        <v>2034</v>
+      </c>
+      <c r="M1">
+        <v>2035</v>
+      </c>
+      <c r="N1">
+        <v>2036</v>
+      </c>
+      <c r="O1">
+        <v>2037</v>
+      </c>
+      <c r="P1">
+        <v>2038</v>
+      </c>
+      <c r="Q1">
+        <v>2039</v>
+      </c>
+      <c r="R1">
+        <v>2040</v>
+      </c>
+      <c r="S1">
+        <v>2041</v>
+      </c>
+      <c r="T1">
+        <v>2042</v>
+      </c>
+      <c r="U1">
+        <v>2043</v>
+      </c>
+      <c r="V1">
+        <v>2044</v>
+      </c>
+      <c r="W1">
+        <v>2045</v>
+      </c>
+      <c r="X1">
+        <v>2046</v>
+      </c>
+      <c r="Y1">
+        <v>2047</v>
+      </c>
+      <c r="Z1">
+        <v>2048</v>
+      </c>
+      <c r="AA1">
+        <v>2049</v>
+      </c>
+      <c r="AB1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="C2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="D2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="E2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="F2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="G2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="H2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="I2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="J2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="K2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="L2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="M2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="N2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="O2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="P2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="Q2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="R2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="S2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="T2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="U2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="V2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="W2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="X2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="Y2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="Z2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="AA2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="AB2">
+        <v>2.9819999999999999E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="C3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="D3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="E3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="F3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="G3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="H3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="I3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="J3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="K3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="L3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="M3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="N3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="O3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="P3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="Q3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="R3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="S3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="T3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="U3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="V3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="W3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="X3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="Y3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="Z3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="AA3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="AB3">
+        <v>2.9819999999999999E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="C4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="D4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="E4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="F4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="G4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="H4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="I4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="J4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="K4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="L4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="M4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="N4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="O4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="P4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="Q4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="R4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="S4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="T4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="U4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="V4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="W4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="X4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="Y4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="Z4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="AA4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="AB4">
+        <v>2.9819999999999999E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="C5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="D5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="E5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="F5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="G5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="H5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="I5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="J5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="K5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="L5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="M5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="N5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="O5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="P5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="Q5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="R5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="S5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="T5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="U5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="V5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="W5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="X5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="Y5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="Z5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="AA5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="AB5">
+        <v>2.9819999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="C6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="D6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="E6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="F6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="G6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="H6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="I6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="J6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="K6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="L6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="M6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="N6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="O6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="P6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="Q6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="R6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="S6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="T6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="U6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="V6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="W6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="X6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="Y6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="Z6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="AA6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="AB6">
+        <v>2.9819999999999999E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="C7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="D7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="E7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="F7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="G7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="H7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="I7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="J7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="K7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="L7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="M7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="N7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="O7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="P7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="Q7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="R7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="S7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="T7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="U7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="V7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="W7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="X7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="Y7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="Z7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="AA7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="AB7">
+        <v>2.9819999999999999E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="C8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="D8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="E8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="F8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="G8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="H8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="I8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="J8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="K8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="L8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="M8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="N8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="O8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="P8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="Q8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="R8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="S8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="T8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="U8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="V8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="W8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="X8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="Y8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="Z8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="AA8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+      <c r="AB8">
+        <v>2.9819999999999999E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65FB1106-E58B-4D47-9864-951943FD7C09}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:AB8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="8" width="14.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1">
+        <v>2024</v>
+      </c>
+      <c r="C1">
+        <v>2025</v>
+      </c>
+      <c r="D1">
+        <v>2026</v>
+      </c>
+      <c r="E1">
+        <v>2027</v>
+      </c>
+      <c r="F1">
+        <v>2028</v>
+      </c>
+      <c r="G1">
+        <v>2029</v>
+      </c>
+      <c r="H1">
+        <v>2030</v>
+      </c>
+      <c r="I1">
+        <v>2031</v>
+      </c>
+      <c r="J1">
+        <v>2032</v>
+      </c>
+      <c r="K1">
+        <v>2033</v>
+      </c>
+      <c r="L1">
+        <v>2034</v>
+      </c>
+      <c r="M1">
+        <v>2035</v>
+      </c>
+      <c r="N1">
+        <v>2036</v>
+      </c>
+      <c r="O1">
+        <v>2037</v>
+      </c>
+      <c r="P1">
+        <v>2038</v>
+      </c>
+      <c r="Q1">
+        <v>2039</v>
+      </c>
+      <c r="R1">
+        <v>2040</v>
+      </c>
+      <c r="S1">
+        <v>2041</v>
+      </c>
+      <c r="T1">
+        <v>2042</v>
+      </c>
+      <c r="U1">
+        <v>2043</v>
+      </c>
+      <c r="V1">
+        <v>2044</v>
+      </c>
+      <c r="W1">
+        <v>2045</v>
+      </c>
+      <c r="X1">
+        <v>2046</v>
+      </c>
+      <c r="Y1">
+        <v>2047</v>
+      </c>
+      <c r="Z1">
+        <v>2048</v>
+      </c>
+      <c r="AA1">
+        <v>2049</v>
+      </c>
+      <c r="AB1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="C2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="D2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="E2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="F2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="G2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="H2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="I2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="J2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="K2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="L2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="M2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="N2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="O2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="P2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="Q2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="R2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="S2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="T2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="U2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="V2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="W2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="X2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="Y2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="Z2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="AA2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="AB2">
+        <v>5.8500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="C3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="D3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="E3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="F3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="G3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="H3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="I3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="J3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="K3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="L3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="M3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="N3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="O3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="P3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="Q3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="R3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="S3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="T3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="U3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="V3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="W3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="X3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="Y3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="Z3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="AA3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="AB3">
+        <v>5.8500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="C4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="D4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="E4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="F4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="G4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="H4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="I4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="J4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="K4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="L4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="M4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="N4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="O4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="P4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="Q4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="R4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="S4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="T4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="U4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="V4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="W4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="X4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="Y4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="Z4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="AA4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="AB4">
+        <v>5.8500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="C5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="D5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="E5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="F5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="G5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="H5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="I5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="J5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="K5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="L5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="M5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="N5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="O5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="P5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="Q5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="R5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="S5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="T5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="U5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="V5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="W5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="X5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="Y5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="Z5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="AA5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="AB5">
+        <v>5.8500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="C6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="D6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="E6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="F6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="G6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="H6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="I6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="J6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="K6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="L6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="M6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="N6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="O6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="P6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="Q6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="R6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="S6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="T6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="U6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="V6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="W6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="X6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="Y6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="Z6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="AA6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="AB6">
+        <v>5.8500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="C7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="D7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="E7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="F7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="G7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="H7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="I7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="J7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="K7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="L7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="M7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="N7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="O7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="P7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="Q7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="R7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="S7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="T7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="U7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="V7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="W7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="X7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="Y7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="Z7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="AA7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="AB7">
+        <v>5.8500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="C8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="D8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="E8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="F8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="G8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="H8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="I8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="J8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="K8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="L8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="M8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="N8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="O8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="P8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="Q8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="R8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="S8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="T8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="U8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="V8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="W8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="X8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="Y8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="Z8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="AA8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+      <c r="AB8">
+        <v>5.8500000000000003E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3718229-5868-451C-82FF-873A3F298CBA}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:AB8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="8" width="14.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1">
+        <v>2024</v>
+      </c>
+      <c r="C1">
+        <v>2025</v>
+      </c>
+      <c r="D1">
+        <v>2026</v>
+      </c>
+      <c r="E1">
+        <v>2027</v>
+      </c>
+      <c r="F1">
+        <v>2028</v>
+      </c>
+      <c r="G1">
+        <v>2029</v>
+      </c>
+      <c r="H1">
+        <v>2030</v>
+      </c>
+      <c r="I1">
+        <v>2031</v>
+      </c>
+      <c r="J1">
+        <v>2032</v>
+      </c>
+      <c r="K1">
+        <v>2033</v>
+      </c>
+      <c r="L1">
+        <v>2034</v>
+      </c>
+      <c r="M1">
+        <v>2035</v>
+      </c>
+      <c r="N1">
+        <v>2036</v>
+      </c>
+      <c r="O1">
+        <v>2037</v>
+      </c>
+      <c r="P1">
+        <v>2038</v>
+      </c>
+      <c r="Q1">
+        <v>2039</v>
+      </c>
+      <c r="R1">
+        <v>2040</v>
+      </c>
+      <c r="S1">
+        <v>2041</v>
+      </c>
+      <c r="T1">
+        <v>2042</v>
+      </c>
+      <c r="U1">
+        <v>2043</v>
+      </c>
+      <c r="V1">
+        <v>2044</v>
+      </c>
+      <c r="W1">
+        <v>2045</v>
+      </c>
+      <c r="X1">
+        <v>2046</v>
+      </c>
+      <c r="Y1">
+        <v>2047</v>
+      </c>
+      <c r="Z1">
+        <v>2048</v>
+      </c>
+      <c r="AA1">
+        <v>2049</v>
+      </c>
+      <c r="AB1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="B2">
         <f>1/17</f>
         <v>5.8823529411764705E-2</v>
       </c>
       <c r="C2">
-        <f t="shared" ref="C2:H2" si="0">1/17</f>
+        <f t="shared" ref="C2:AB8" si="0">1/17</f>
         <v>5.8823529411764705E-2</v>
       </c>
       <c r="D2">
@@ -812,142 +7897,1657 @@
         <f t="shared" si="0"/>
         <v>5.8823529411764705E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="I2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="J2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="K2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="L2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="M2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="N2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="O2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="P2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Q2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="R2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="S2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="T2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="U2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="V2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="W2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="X2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Y2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Z2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AA2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AB2">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <f>1/17</f>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="C3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="D3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="E3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="F3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="G3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="H3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="I3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="J3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="K3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="L3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="M3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="N3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="O3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="P3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="R3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="S3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="T3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="U3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="V3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="W3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="X3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Y3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Z3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AA3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AB3">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <f>1/17</f>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="P4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="S4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="V4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="W4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="X4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Y4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Z4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AA4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AB4">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <f>1/17</f>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="W5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="X5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Y5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Z5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AA5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AB5">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
+        <f>1/17</f>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="W6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="X6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Y6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Z6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AA6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AB6">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
+        <f>1/17</f>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="W7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="X7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Y7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Z7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AA7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AB7">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <f>1/17</f>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="X8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="Z8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AA8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+      <c r="AB8">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3693935-1AA0-41BB-8C80-C3C126780DEA}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:AB8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="8" width="14.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:28" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1">
+        <v>2024</v>
+      </c>
+      <c r="C1">
+        <v>2025</v>
+      </c>
+      <c r="D1">
+        <v>2026</v>
+      </c>
+      <c r="E1">
+        <v>2027</v>
+      </c>
+      <c r="F1">
+        <v>2028</v>
+      </c>
+      <c r="G1">
+        <v>2029</v>
+      </c>
+      <c r="H1">
+        <v>2030</v>
+      </c>
+      <c r="I1">
+        <v>2031</v>
+      </c>
+      <c r="J1">
+        <v>2032</v>
+      </c>
+      <c r="K1">
+        <v>2033</v>
+      </c>
+      <c r="L1">
+        <v>2034</v>
+      </c>
+      <c r="M1">
+        <v>2035</v>
+      </c>
+      <c r="N1">
+        <v>2036</v>
+      </c>
+      <c r="O1">
+        <v>2037</v>
+      </c>
+      <c r="P1">
+        <v>2038</v>
+      </c>
+      <c r="Q1">
+        <v>2039</v>
+      </c>
+      <c r="R1">
+        <v>2040</v>
+      </c>
+      <c r="S1">
+        <v>2041</v>
+      </c>
+      <c r="T1">
+        <v>2042</v>
+      </c>
+      <c r="U1">
+        <v>2043</v>
+      </c>
+      <c r="V1">
+        <v>2044</v>
+      </c>
+      <c r="W1">
+        <v>2045</v>
+      </c>
+      <c r="X1">
+        <v>2046</v>
+      </c>
+      <c r="Y1">
+        <v>2047</v>
+      </c>
+      <c r="Z1">
+        <v>2048</v>
+      </c>
+      <c r="AA1">
+        <v>2049</v>
+      </c>
+      <c r="AB1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>13</v>
+      </c>
+      <c r="B2">
+        <f>1/19</f>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="C2">
+        <f t="shared" ref="C2:AB8" si="0">1/19</f>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="D2">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="E2">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="F2">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="G2">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="H2">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="I2">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="J2">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="K2">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="L2">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="M2">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="N2">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="O2">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="P2">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="Q2">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="R2">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="S2">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="T2">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="U2">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="V2">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="W2">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="X2">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="Y2">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="Z2">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="AA2">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="AB2">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="B3">
         <f>1/19</f>
         <v>5.2631578947368418E-2</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:H3" si="1">1/19</f>
+        <f t="shared" si="0"/>
         <v>5.2631578947368418E-2</v>
       </c>
       <c r="D3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5.2631578947368418E-2</v>
       </c>
       <c r="E3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5.2631578947368418E-2</v>
       </c>
       <c r="F3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5.2631578947368418E-2</v>
       </c>
       <c r="G3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5.2631578947368418E-2</v>
       </c>
       <c r="H3">
-        <f t="shared" si="1"/>
-        <v>5.2631578947368418E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="I3">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="J3">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="K3">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="L3">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="M3">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="N3">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="O3">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="P3">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="R3">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="S3">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="T3">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="U3">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="V3">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="W3">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="X3">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="Y3">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="Z3">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="AA3">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="AB3">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="B4">
-        <v>2.8000000000000001E-2</v>
+        <f>1/19</f>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="C4">
-        <v>2.8000000000000001E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="D4">
-        <v>2.8000000000000001E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="E4">
-        <v>2.8000000000000001E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="F4">
-        <v>2.8000000000000001E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="G4">
-        <v>2.8000000000000001E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="H4">
-        <v>2.8000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>15</v>
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="P4">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="S4">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="V4">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="W4">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="X4">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="Y4">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="Z4">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="AA4">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="AB4">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="B5">
-        <v>2.9000000000000001E-2</v>
+        <f>1/19</f>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="C5">
-        <v>2.9000000000000001E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="D5">
-        <v>2.9000000000000001E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="E5">
-        <v>2.9000000000000001E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="F5">
-        <v>2.9000000000000001E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="G5">
-        <v>2.9000000000000001E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="H5">
-        <v>2.9000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>16</v>
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="W5">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="X5">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="Y5">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="Z5">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="AA5">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="AB5">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="B6">
-        <v>3.0300000000000001E-2</v>
+        <f>1/19</f>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="C6">
-        <v>3.0300000000000001E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="D6">
-        <v>3.0300000000000001E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="E6">
-        <v>3.0300000000000001E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="F6">
-        <v>3.0300000000000001E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="G6">
-        <v>3.0300000000000001E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="H6">
-        <v>3.0300000000000001E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>17</v>
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="W6">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="X6">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="Y6">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="Z6">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="AA6">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="AB6">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <f>1/19</f>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="W7">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="X7">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="Y7">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="Z7">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="AA7">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="AB7">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <f>1/19</f>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="X8">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="Z8">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="AA8">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="AB8">
+        <f t="shared" si="0"/>
+        <v>5.2631578947368418E-2</v>
       </c>
     </row>
   </sheetData>
